--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ25"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,44 +787,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72871277</v>
+        <v>135775416</v>
       </c>
       <c r="B3" t="n">
-        <v>99038</v>
+        <v>57396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>102961</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Korsmossen, Vstm</t>
+          <t>Viludden, Gunnilbo sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544388</v>
+        <v>549956</v>
       </c>
       <c r="R3" t="n">
-        <v>6636504</v>
+        <v>6637776</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,22 +859,27 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Skinnskatteberg</t>
+          <t>Gunnilbo</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-06-18</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-06-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med exemplar.</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,37 +890,28 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Håkan Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Håkan Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72871277</t>
+          <t>https://artportalen.se/Sighting/135775416</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121430737</v>
+        <v>72871277</v>
       </c>
       <c r="B4" t="n">
         <v>99038</v>
@@ -923,21 +935,17 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bockhammar, Vstm</t>
+          <t>Korsmossen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544326</v>
+        <v>544388</v>
       </c>
       <c r="R4" t="n">
-        <v>6636545</v>
+        <v>6636504</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,12 +972,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2018-06-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2018-06-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med exemplar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,31 +993,40 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Leif Andersson, Robert Ennerfelt</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121430737</t>
+          <t>https://artportalen.se/Sighting/72871277</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>72871274</v>
+        <v>121430737</v>
       </c>
       <c r="B5" t="n">
-        <v>99156</v>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,34 +1034,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219875</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Römossen, Vstm</t>
+          <t>Bockhammar, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542652</v>
+        <v>544326</v>
       </c>
       <c r="R5" t="n">
-        <v>6635935</v>
+        <v>6636545</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,17 +1088,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-06-18</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-06-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flertalet exemplar.</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,78 +1104,69 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Anna-Lotta Hellqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Anna-Lotta Hellqvist, Leif Andersson, Robert Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72871274</t>
+          <t>https://artportalen.se/Sighting/121430737</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129386023</v>
+        <v>72871274</v>
       </c>
       <c r="B6" t="n">
-        <v>87195</v>
+        <v>99156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>426</v>
+        <v>219875</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bastnäsområdet, Vstm</t>
+          <t>Römossen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533167</v>
+        <v>542652</v>
       </c>
       <c r="R6" t="n">
-        <v>6635150</v>
+        <v>6635935</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,12 +1190,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2018-06-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2018-06-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flertalet exemplar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,55 +1211,64 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129386023</t>
+          <t>https://artportalen.se/Sighting/72871274</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129385996</v>
+        <v>129386023</v>
       </c>
       <c r="B7" t="n">
-        <v>87412</v>
+        <v>87195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3624</v>
+        <v>426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Cortinarius aureofulvus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1254,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533169</v>
+        <v>533167</v>
       </c>
       <c r="R7" t="n">
-        <v>6635149</v>
+        <v>6635150</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,40 +1341,36 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129385996</t>
+          <t>https://artportalen.se/Sighting/129386023</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129386038</v>
+        <v>129385996</v>
       </c>
       <c r="B8" t="n">
-        <v>87353</v>
+        <v>87412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3721</v>
+        <v>3624</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåbrun spindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius serarius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1363,7 +1381,7 @@
         <v>533169</v>
       </c>
       <c r="R8" t="n">
-        <v>6635150</v>
+        <v>6635149</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,38 +1443,38 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129386038</t>
+          <t>https://artportalen.se/Sighting/129385996</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129386029</v>
+        <v>129386038</v>
       </c>
       <c r="B9" t="n">
-        <v>93215</v>
+        <v>87353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4368</v>
+        <v>3721</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blåbrun spindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius serarius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1466,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533168</v>
+        <v>533169</v>
       </c>
       <c r="R9" t="n">
-        <v>6635105</v>
+        <v>6635150</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,16 +1549,16 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129386029</t>
+          <t>https://artportalen.se/Sighting/129386038</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129930380</v>
+        <v>129386029</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>93215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,38 +1566,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4368</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sunnanfors, Vstm</t>
+          <t>Bastnäsområdet, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534800</v>
+        <v>533168</v>
       </c>
       <c r="R10" t="n">
-        <v>6634666</v>
+        <v>6635105</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,17 +1620,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,27 +1640,31 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129930380</t>
+          <t>https://artportalen.se/Sighting/129386029</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111537628</v>
+        <v>129930380</v>
       </c>
       <c r="B11" t="n">
-        <v>43258</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,16 +1672,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>201129</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycaena virgaureae</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1683,17 +1696,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skinnskatteberg, Vstm</t>
+          <t>Sunnanfors, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529631</v>
+        <v>534800</v>
       </c>
       <c r="R11" t="n">
-        <v>6634446</v>
+        <v>6634666</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1717,12 +1730,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1737,73 +1755,69 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Margaux Boeraeve</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Margaux Boeraeve</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111537628</t>
+          <t>https://artportalen.se/Sighting/129930380</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125096542</v>
+        <v>111537628</v>
       </c>
       <c r="B12" t="n">
-        <v>106244</v>
+        <v>43258</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>201129</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kärrgeten , Vstm</t>
+          <t>Skinnskatteberg, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535487</v>
+        <v>529631</v>
       </c>
       <c r="R12" t="n">
-        <v>6633995</v>
+        <v>6634446</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,12 +1841,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,34 +1855,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alice  Hultgren</t>
+          <t>Margaux Boeraeve</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alice  Hultgren</t>
+          <t>Margaux Boeraeve</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125096542</t>
+          <t>https://artportalen.se/Sighting/111537628</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>61788690</v>
+        <v>125096542</v>
       </c>
       <c r="B13" t="n">
-        <v>97989</v>
+        <v>106244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1876,37 +1889,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skilån, Paddtjärnarna, Vstm</t>
+          <t>Kärrgeten , Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527365</v>
+        <v>535487</v>
       </c>
       <c r="R13" t="n">
-        <v>6632674</v>
+        <v>6633995</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1930,17 +1951,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2016-10-07</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2016-10-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,35 +1965,31 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Tallskog, ung</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Alice  Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Alice  Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61788690</t>
+          <t>https://artportalen.se/Sighting/125096542</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>61788692</v>
+        <v>61788690</v>
       </c>
       <c r="B14" t="n">
         <v>97989</v>
@@ -2015,7 +2027,7 @@
         <v>527365</v>
       </c>
       <c r="R14" t="n">
-        <v>6632655</v>
+        <v>6632674</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,16 +2095,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61788692</t>
+          <t>https://artportalen.se/Sighting/61788690</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>61788691</v>
+        <v>61788692</v>
       </c>
       <c r="B15" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,16 +2112,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2127,7 +2139,7 @@
         <v>527365</v>
       </c>
       <c r="R15" t="n">
-        <v>6632674</v>
+        <v>6632655</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,6 +2174,11 @@
           <t>2016-10-07</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2190,13 +2207,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61788691</t>
+          <t>https://artportalen.se/Sighting/61788692</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>61788693</v>
+        <v>61788691</v>
       </c>
       <c r="B16" t="n">
         <v>97983</v>
@@ -2234,7 +2251,7 @@
         <v>527365</v>
       </c>
       <c r="R16" t="n">
-        <v>6632655</v>
+        <v>6632674</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,13 +2314,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61788693</t>
+          <t>https://artportalen.se/Sighting/61788691</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>61788697</v>
+        <v>61788693</v>
       </c>
       <c r="B17" t="n">
         <v>97983</v>
@@ -2338,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527376</v>
+        <v>527365</v>
       </c>
       <c r="R17" t="n">
-        <v>6632624</v>
+        <v>6632655</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2404,13 +2421,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61788697</t>
+          <t>https://artportalen.se/Sighting/61788693</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>61788699</v>
+        <v>61788697</v>
       </c>
       <c r="B18" t="n">
         <v>97983</v>
@@ -2448,7 +2465,7 @@
         <v>527376</v>
       </c>
       <c r="R18" t="n">
-        <v>6632555</v>
+        <v>6632624</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,11 +2500,6 @@
           <t>2016-10-07</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2516,16 +2528,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61788699</t>
+          <t>https://artportalen.se/Sighting/61788697</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>61788683</v>
+        <v>61788699</v>
       </c>
       <c r="B19" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,16 +2545,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2557,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527485</v>
+        <v>527376</v>
       </c>
       <c r="R19" t="n">
-        <v>6632676</v>
+        <v>6632555</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,6 +2607,11 @@
           <t>2016-10-07</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2606,7 +2623,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Myrkant vid tjärn</t>
+          <t>Tallskog, ung</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2623,13 +2640,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61788683</t>
+          <t>https://artportalen.se/Sighting/61788699</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>61788700</v>
+        <v>61788683</v>
       </c>
       <c r="B20" t="n">
         <v>97986</v>
@@ -2664,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527386</v>
+        <v>527485</v>
       </c>
       <c r="R20" t="n">
-        <v>6632595</v>
+        <v>6632676</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2713,7 +2730,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Tallskog, ung</t>
+          <t>Myrkant vid tjärn</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2730,13 +2747,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61788700</t>
+          <t>https://artportalen.se/Sighting/61788683</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>61788701</v>
+        <v>61788700</v>
       </c>
       <c r="B21" t="n">
         <v>97986</v>
@@ -2771,10 +2788,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527336</v>
+        <v>527386</v>
       </c>
       <c r="R21" t="n">
-        <v>6632604</v>
+        <v>6632595</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,54 +2854,54 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61788701</t>
+          <t>https://artportalen.se/Sighting/61788700</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>75360630</v>
+        <v>61788701</v>
       </c>
       <c r="B22" t="n">
-        <v>93189</v>
+        <v>97986</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>221946</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lien, S, Vstm</t>
+          <t>Skilån, Paddtjärnarna, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528045</v>
+        <v>527336</v>
       </c>
       <c r="R22" t="n">
-        <v>6629670</v>
+        <v>6632604</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2908,12 +2925,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2018-10-17</t>
+          <t>2016-10-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2018-10-17</t>
+          <t>2016-10-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2927,59 +2944,55 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>sandtallskog</t>
+          <t>Tallskog, ung</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Svampinventering i sandtallskogar</t>
-        </is>
-      </c>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75360630</t>
+          <t>https://artportalen.se/Sighting/61788701</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>75360629</v>
+        <v>75360630</v>
       </c>
       <c r="B23" t="n">
-        <v>93193</v>
+        <v>93189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4363</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2989,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528048</v>
+        <v>528045</v>
       </c>
       <c r="R23" t="n">
-        <v>6629674</v>
+        <v>6629670</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3059,66 +3072,54 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75360629</t>
+          <t>https://artportalen.se/Sighting/75360630</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132761003</v>
+        <v>75360629</v>
       </c>
       <c r="B24" t="n">
-        <v>56539</v>
+        <v>93193</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>206004</v>
+        <v>4363</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bjurfors gamla tomt, Vstm</t>
+          <t>Lien, S, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546211</v>
+        <v>528048</v>
       </c>
       <c r="R24" t="n">
-        <v>6628964</v>
+        <v>6629674</v>
       </c>
       <c r="S24" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3137,27 +3138,17 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Gunnilbo</t>
+          <t>Skinnskatteberg</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2018-10-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2018-10-17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3168,31 +3159,40 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>sandtallskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Svampinventering i sandtallskogar</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132761003</t>
+          <t>https://artportalen.se/Sighting/75360629</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113273795</v>
+        <v>132761003</v>
       </c>
       <c r="B25" t="n">
-        <v>79946</v>
+        <v>56539</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,37 +3200,49 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>206004</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra kavelbromossen, Vstm</t>
+          <t>Bjurfors gamla tomt, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>535096</v>
+        <v>546211</v>
       </c>
       <c r="R25" t="n">
-        <v>6625338</v>
+        <v>6628964</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3249,17 +3261,27 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Skinnskatteberg</t>
+          <t>Gunnilbo</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3270,29 +3292,131 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>tallstubbe</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132761003</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>113273795</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Södra kavelbromossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>535096</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6625338</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-08-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>tallstubbe</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AX26" t="inlineStr">
         <is>
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr">
+      <c r="AY26" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113273795</t>
         </is>
@@ -3324,6 +3448,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135775416</v>
       </c>
       <c r="B3" t="n">
-        <v>57396</v>
+        <v>57398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135775416</v>
       </c>
       <c r="B3" t="n">
-        <v>57398</v>
+        <v>57399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135775416</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135775416</v>
       </c>
       <c r="B3" t="n">
-        <v>57403</v>
+        <v>57404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 482-2024 artfynd.xlsx
+++ b/artfynd/S 482-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135775416</v>
       </c>
       <c r="B3" t="n">
-        <v>57404</v>
+        <v>57409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
